--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -16,12 +16,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$-409]dd-mmm-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd-mmm hh:mm"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="[$-409]dd-mmm-yyyy hh:mm"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +62,11 @@
       <b val="1"/>
       <color rgb="0016324F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -165,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,10 +244,41 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,9 +287,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -708,16 +742,16 @@
       <c r="C4" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="44" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="44" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="44" t="n">
         <v>46303.5</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="28">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
@@ -742,16 +776,16 @@
       <c r="C5" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="44" t="n">
         <v>46302.41666666666</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="44" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="44" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="28">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
@@ -776,16 +810,16 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="44" t="n">
         <v>46303.75</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="44" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="44" t="n">
         <v>46305.625</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="28">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
@@ -810,16 +844,16 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="44" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="44" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="44" t="n">
         <v>46306.625</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="28">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
@@ -844,16 +878,16 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="44" t="n">
         <v>46300.875</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="44" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="44" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="28">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
@@ -878,16 +912,16 @@
       <c r="C9" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="44" t="n">
         <v>46302.625</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="44" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="44" t="n">
         <v>46304.70833333334</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="28">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -912,16 +946,16 @@
       <c r="C10" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="44" t="n">
         <v>46304.375</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="44" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="44" t="n">
         <v>46306.58333333334</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="28">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -946,16 +980,16 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="44" t="n">
         <v>46301.875</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="44" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="44" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="28">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -980,16 +1014,16 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="44" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="44" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="44" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="28">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1014,16 +1048,16 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="44" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="44" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="44" t="n">
         <v>46306.04166666666</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="28">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
@@ -1048,16 +1082,16 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="44" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="44" t="n">
         <v>46306.16666666666</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="44" t="n">
         <v>46307.54166666666</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="28">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
@@ -1082,16 +1116,16 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="44" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="44" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F15" s="44" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="28">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
@@ -1116,16 +1150,16 @@
       <c r="C16" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="44" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="44" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="44" t="n">
         <v>46305.54166666666</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="28">
         <f>(F16-E16)*24</f>
         <v/>
       </c>
@@ -1150,16 +1184,16 @@
       <c r="C17" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="44" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="E17" s="44" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F17" s="33" t="n">
+      <c r="F17" s="44" t="n">
         <v>46306.25</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="28">
         <f>(F17-E17)*24</f>
         <v/>
       </c>
@@ -1184,16 +1218,16 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="44" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E18" s="33" t="n">
+      <c r="E18" s="44" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F18" s="33" t="n">
+      <c r="F18" s="44" t="n">
         <v>46307.58333333334</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="28">
         <f>(F18-E18)*24</f>
         <v/>
       </c>
@@ -1218,16 +1252,16 @@
       <c r="C19" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="44" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E19" s="44" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="44" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="28">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1252,16 +1286,16 @@
       <c r="C20" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="44" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E20" s="33" t="n">
+      <c r="E20" s="44" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F20" s="33" t="n">
+      <c r="F20" s="44" t="n">
         <v>46306.125</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="28">
         <f>(F20-E20)*24</f>
         <v/>
       </c>
@@ -1286,16 +1320,16 @@
       <c r="C21" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="44" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E21" s="33" t="n">
+      <c r="E21" s="44" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F21" s="33" t="n">
+      <c r="F21" s="44" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="28">
         <f>(F21-E21)*24</f>
         <v/>
       </c>
@@ -1320,16 +1354,16 @@
       <c r="C22" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="44" t="n">
         <v>46302.79166666666</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="E22" s="44" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="F22" s="33" t="n">
+      <c r="F22" s="44" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="28">
         <f>(F22-E22)*24</f>
         <v/>
       </c>
@@ -1341,7 +1375,7 @@
       <c r="I22" s="23" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1374,9 +1408,9 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="29" t="n"/>
-      <c r="I26" s="30" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="40" t="n"/>
+      <c r="I26" s="41" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -1389,11 +1423,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="35" t="n">
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="45" t="n">
         <v>46299</v>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="45" t="n">
         <v>46319</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -1401,9 +1435,9 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (MTT BANGKOK has been alongside at 20D since 07/14, HE JIN shifts in on 09/02)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="29" t="n"/>
-      <c r="I27" s="30" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="40" t="n"/>
+      <c r="I27" s="41" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
@@ -1416,11 +1450,11 @@
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="36" t="n">
+      <c r="C28" s="42" t="n"/>
+      <c r="D28" s="46" t="n">
         <v>46300</v>
       </c>
-      <c r="E28" s="36" t="n">
+      <c r="E28" s="46" t="n">
         <v>46313</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -1428,9 +1462,9 @@
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G28" s="29" t="n"/>
-      <c r="H28" s="29" t="n"/>
-      <c r="I28" s="30" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="40" t="n"/>
+      <c r="I28" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -251,6 +251,12 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -261,12 +267,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -251,22 +251,22 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -669,9 +669,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,15 +715,20 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Waiting for Berth (h)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Hours Alongside</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Marked</t>
         </is>
@@ -752,15 +758,19 @@
         <v>46303.5</v>
       </c>
       <c r="G4" s="28">
+        <f>(E4-D4)*24</f>
+        <v/>
+      </c>
+      <c r="H4" s="28">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I4" s="23" t="inlineStr"/>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -786,15 +796,19 @@
         <v>46304.58333333334</v>
       </c>
       <c r="G5" s="28">
+        <f>(E5-D5)*24</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="inlineStr"/>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -820,15 +834,19 @@
         <v>46305.625</v>
       </c>
       <c r="G6" s="28">
+        <f>(E6-D6)*24</f>
+        <v/>
+      </c>
+      <c r="H6" s="28">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr"/>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -854,15 +872,19 @@
         <v>46306.625</v>
       </c>
       <c r="G7" s="28">
+        <f>(E7-D7)*24</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr"/>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -888,15 +910,19 @@
         <v>46303.54166666666</v>
       </c>
       <c r="G8" s="28">
+        <f>(E8-D8)*24</f>
+        <v/>
+      </c>
+      <c r="H8" s="28">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr"/>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -922,15 +948,19 @@
         <v>46304.70833333334</v>
       </c>
       <c r="G9" s="28">
+        <f>(E9-D9)*24</f>
+        <v/>
+      </c>
+      <c r="H9" s="28">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr"/>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -956,15 +986,19 @@
         <v>46306.58333333334</v>
       </c>
       <c r="G10" s="28">
+        <f>(E10-D10)*24</f>
+        <v/>
+      </c>
+      <c r="H10" s="28">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr"/>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -990,15 +1024,19 @@
         <v>46303.54166666666</v>
       </c>
       <c r="G11" s="28">
+        <f>(E11-D11)*24</f>
+        <v/>
+      </c>
+      <c r="H11" s="28">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr"/>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1024,15 +1062,19 @@
         <v>46304.58333333334</v>
       </c>
       <c r="G12" s="28">
+        <f>(E12-D12)*24</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="inlineStr"/>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1058,15 +1100,19 @@
         <v>46306.04166666666</v>
       </c>
       <c r="G13" s="28">
+        <f>(E13-D13)*24</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr"/>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1092,15 +1138,19 @@
         <v>46307.54166666666</v>
       </c>
       <c r="G14" s="28">
+        <f>(E14-D14)*24</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I14" s="23" t="inlineStr"/>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1126,15 +1176,19 @@
         <v>46304.08333333334</v>
       </c>
       <c r="G15" s="28">
+        <f>(E15-D15)*24</f>
+        <v/>
+      </c>
+      <c r="H15" s="28">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="inlineStr"/>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1160,15 +1214,19 @@
         <v>46305.54166666666</v>
       </c>
       <c r="G16" s="28">
+        <f>(E16-D16)*24</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
         <f>(F16-E16)*24</f>
         <v/>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I16" s="23" t="inlineStr"/>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1194,15 +1252,19 @@
         <v>46306.25</v>
       </c>
       <c r="G17" s="28">
+        <f>(E17-D17)*24</f>
+        <v/>
+      </c>
+      <c r="H17" s="28">
         <f>(F17-E17)*24</f>
         <v/>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr"/>
+      <c r="J17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1228,15 +1290,19 @@
         <v>46307.58333333334</v>
       </c>
       <c r="G18" s="28">
+        <f>(E18-D18)*24</f>
+        <v/>
+      </c>
+      <c r="H18" s="28">
         <f>(F18-E18)*24</f>
         <v/>
       </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr"/>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1262,15 +1328,19 @@
         <v>46304.54166666666</v>
       </c>
       <c r="G19" s="28">
+        <f>(E19-D19)*24</f>
+        <v/>
+      </c>
+      <c r="H19" s="28">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr"/>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1296,15 +1366,19 @@
         <v>46306.125</v>
       </c>
       <c r="G20" s="28">
+        <f>(E20-D20)*24</f>
+        <v/>
+      </c>
+      <c r="H20" s="28">
         <f>(F20-E20)*24</f>
         <v/>
       </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr"/>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1330,15 +1404,19 @@
         <v>46307.08333333334</v>
       </c>
       <c r="G21" s="28">
+        <f>(E21-D21)*24</f>
+        <v/>
+      </c>
+      <c r="H21" s="28">
         <f>(F21-E21)*24</f>
         <v/>
       </c>
-      <c r="H21" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I21" s="23" t="inlineStr"/>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1364,15 +1442,19 @@
         <v>46304.08333333334</v>
       </c>
       <c r="G22" s="28">
+        <f>(E22-D22)*24</f>
+        <v/>
+      </c>
+      <c r="H22" s="28">
         <f>(F22-E22)*24</f>
         <v/>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>20D</t>
         </is>
       </c>
-      <c r="I22" s="23" t="inlineStr"/>
+      <c r="J22" s="23" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="39" t="inlineStr">
@@ -1410,7 +1492,8 @@
       </c>
       <c r="G26" s="40" t="n"/>
       <c r="H26" s="40" t="n"/>
-      <c r="I26" s="41" t="n"/>
+      <c r="I26" s="40" t="n"/>
+      <c r="J26" s="41" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -1437,7 +1520,8 @@
       </c>
       <c r="G27" s="40" t="n"/>
       <c r="H27" s="40" t="n"/>
-      <c r="I27" s="41" t="n"/>
+      <c r="I27" s="40" t="n"/>
+      <c r="J27" s="41" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
@@ -1464,13 +1548,14 @@
       </c>
       <c r="G28" s="40" t="n"/>
       <c r="H28" s="40" t="n"/>
-      <c r="I28" s="41" t="n"/>
+      <c r="I28" s="40" t="n"/>
+      <c r="J28" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="F27:J27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -223,22 +223,7 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,6 +233,9 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -255,6 +243,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,17 +263,8 @@
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -290,9 +275,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -748,20 +730,20 @@
       <c r="C4" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D4" s="44" t="n">
+      <c r="D4" s="39" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="E4" s="44" t="n">
+      <c r="E4" s="39" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F4" s="44" t="n">
+      <c r="F4" s="39" t="n">
         <v>46303.5</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="24">
         <f>(E4-D4)*24</f>
         <v/>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="24">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
@@ -786,20 +768,20 @@
       <c r="C5" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="39" t="n">
         <v>46302.41666666666</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="39" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="39" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="24">
         <f>(E5-D5)*24</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="24">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
@@ -824,20 +806,20 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="39" t="n">
         <v>46303.75</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="39" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="39" t="n">
         <v>46305.625</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="24">
         <f>(E6-D6)*24</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="24">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
@@ -862,20 +844,20 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="39" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="39" t="n">
         <v>46306.625</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="24">
         <f>(E7-D7)*24</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="24">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
@@ -900,20 +882,20 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="39" t="n">
         <v>46300.875</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="39" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="24">
         <f>(E8-D8)*24</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="24">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
@@ -938,20 +920,20 @@
       <c r="C9" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="39" t="n">
         <v>46302.625</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="39" t="n">
         <v>46304.70833333334</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="24">
         <f>(E9-D9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="24">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -976,20 +958,20 @@
       <c r="C10" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="39" t="n">
         <v>46304.375</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="39" t="n">
         <v>46306.58333333334</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="24">
         <f>(E10-D10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="24">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1014,20 +996,20 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="39" t="n">
         <v>46301.875</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="39" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="24">
         <f>(E11-D11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="24">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1052,20 +1034,20 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="39" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="39" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="24">
         <f>(E12-D12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="24">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1090,20 +1072,20 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="39" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="39" t="n">
         <v>46306.04166666666</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="24">
         <f>(E13-D13)*24</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="24">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
@@ -1128,20 +1110,20 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="39" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="39" t="n">
         <v>46306.16666666666</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="39" t="n">
         <v>46307.54166666666</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="24">
         <f>(E14-D14)*24</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="24">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
@@ -1166,20 +1148,20 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="39" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="39" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="39" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="24">
         <f>(E15-D15)*24</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="24">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
@@ -1204,20 +1186,20 @@
       <c r="C16" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="39" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="E16" s="44" t="n">
+      <c r="E16" s="39" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="39" t="n">
         <v>46305.54166666666</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="24">
         <f>(E16-D16)*24</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="24">
         <f>(F16-E16)*24</f>
         <v/>
       </c>
@@ -1242,20 +1224,20 @@
       <c r="C17" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="39" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="39" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="39" t="n">
         <v>46306.25</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="24">
         <f>(E17-D17)*24</f>
         <v/>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="24">
         <f>(F17-E17)*24</f>
         <v/>
       </c>
@@ -1280,20 +1262,20 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="39" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E18" s="39" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="39" t="n">
         <v>46307.58333333334</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="24">
         <f>(E18-D18)*24</f>
         <v/>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="24">
         <f>(F18-E18)*24</f>
         <v/>
       </c>
@@ -1318,20 +1300,20 @@
       <c r="C19" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="44" t="n">
+      <c r="D19" s="39" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E19" s="44" t="n">
+      <c r="E19" s="39" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F19" s="44" t="n">
+      <c r="F19" s="39" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="24">
         <f>(E19-D19)*24</f>
         <v/>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="24">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1356,20 +1338,20 @@
       <c r="C20" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="44" t="n">
+      <c r="D20" s="39" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E20" s="44" t="n">
+      <c r="E20" s="39" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F20" s="44" t="n">
+      <c r="F20" s="39" t="n">
         <v>46306.125</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="24">
         <f>(E20-D20)*24</f>
         <v/>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="24">
         <f>(F20-E20)*24</f>
         <v/>
       </c>
@@ -1394,20 +1376,20 @@
       <c r="C21" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="39" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E21" s="44" t="n">
+      <c r="E21" s="39" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F21" s="44" t="n">
+      <c r="F21" s="39" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="24">
         <f>(E21-D21)*24</f>
         <v/>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="24">
         <f>(F21-E21)*24</f>
         <v/>
       </c>
@@ -1432,20 +1414,20 @@
       <c r="C22" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="39" t="n">
         <v>46302.79166666666</v>
       </c>
-      <c r="E22" s="44" t="n">
+      <c r="E22" s="39" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="F22" s="44" t="n">
+      <c r="F22" s="39" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="24">
         <f>(E22-D22)*24</f>
         <v/>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="24">
         <f>(F22-E22)*24</f>
         <v/>
       </c>
@@ -1457,7 +1439,7 @@
       <c r="J22" s="23" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1490,10 +1472,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G26" s="40" t="n"/>
-      <c r="H26" s="40" t="n"/>
-      <c r="I26" s="40" t="n"/>
-      <c r="J26" s="41" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="36" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -1506,11 +1488,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="45" t="n">
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="40" t="n">
         <v>46299</v>
       </c>
-      <c r="E27" s="45" t="n">
+      <c r="E27" s="40" t="n">
         <v>46319</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -1518,38 +1500,38 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (MTT BANGKOK has been alongside at 20D since 07/14, HE JIN shifts in on 09/02)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G27" s="40" t="n"/>
-      <c r="H27" s="40" t="n"/>
-      <c r="I27" s="40" t="n"/>
-      <c r="J27" s="41" t="n"/>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="35" t="n"/>
+      <c r="J27" s="36" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>20E / G.25</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C28" s="42" t="n"/>
-      <c r="D28" s="46" t="n">
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="40" t="n">
         <v>46300</v>
       </c>
-      <c r="E28" s="46" t="n">
+      <c r="E28" s="40" t="n">
         <v>46313</v>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G28" s="40" t="n"/>
-      <c r="H28" s="40" t="n"/>
-      <c r="I28" s="40" t="n"/>
-      <c r="J28" s="41" t="n"/>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="35" t="n"/>
+      <c r="I28" s="35" t="n"/>
+      <c r="J28" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="[$-409]dd-mmm-yyyy hh:mm"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,11 @@
       <b val="1"/>
       <color rgb="0016324F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -171,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,7 +235,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,29 +253,30 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -730,13 +736,13 @@
       <c r="C4" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="40" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="E4" s="39" t="n">
+      <c r="E4" s="40" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="40" t="n">
         <v>46303.5</v>
       </c>
       <c r="G4" s="24">
@@ -768,13 +774,13 @@
       <c r="C5" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="40" t="n">
         <v>46302.41666666666</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="40" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="40" t="n">
         <v>46304.58333333334</v>
       </c>
       <c r="G5" s="24">
@@ -806,13 +812,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="40" t="n">
         <v>46303.75</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="40" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="40" t="n">
         <v>46305.625</v>
       </c>
       <c r="G6" s="24">
@@ -844,13 +850,13 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="40" t="n">
         <v>46306.625</v>
       </c>
       <c r="G7" s="24">
@@ -882,13 +888,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <v>46300.875</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="40" t="n">
         <v>46303.54166666666</v>
       </c>
       <c r="G8" s="24">
@@ -920,13 +926,13 @@
       <c r="C9" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <v>46302.625</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="40" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="40" t="n">
         <v>46304.70833333334</v>
       </c>
       <c r="G9" s="24">
@@ -958,13 +964,13 @@
       <c r="C10" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="40" t="n">
         <v>46304.375</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="40" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="40" t="n">
         <v>46306.58333333334</v>
       </c>
       <c r="G10" s="24">
@@ -996,13 +1002,13 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="40" t="n">
         <v>46301.875</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="40" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="40" t="n">
         <v>46303.54166666666</v>
       </c>
       <c r="G11" s="24">
@@ -1034,13 +1040,13 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="40" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="40" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="40" t="n">
         <v>46304.58333333334</v>
       </c>
       <c r="G12" s="24">
@@ -1072,13 +1078,13 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="40" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="40" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="40" t="n">
         <v>46306.04166666666</v>
       </c>
       <c r="G13" s="24">
@@ -1110,13 +1116,13 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="40" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="40" t="n">
         <v>46306.16666666666</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="40" t="n">
         <v>46307.54166666666</v>
       </c>
       <c r="G14" s="24">
@@ -1148,13 +1154,13 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="40" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="40" t="n">
         <v>46304.08333333334</v>
       </c>
       <c r="G15" s="24">
@@ -1186,13 +1192,13 @@
       <c r="C16" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="40" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="40" t="n">
         <v>46305.54166666666</v>
       </c>
       <c r="G16" s="24">
@@ -1224,13 +1230,13 @@
       <c r="C17" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="40" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="40" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="40" t="n">
         <v>46306.25</v>
       </c>
       <c r="G17" s="24">
@@ -1262,13 +1268,13 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="40" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="40" t="n">
         <v>46307.58333333334</v>
       </c>
       <c r="G18" s="24">
@@ -1300,13 +1306,13 @@
       <c r="C19" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="40" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="40" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="40" t="n">
         <v>46304.54166666666</v>
       </c>
       <c r="G19" s="24">
@@ -1338,13 +1344,13 @@
       <c r="C20" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="40" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E20" s="39" t="n">
+      <c r="E20" s="40" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F20" s="39" t="n">
+      <c r="F20" s="40" t="n">
         <v>46306.125</v>
       </c>
       <c r="G20" s="24">
@@ -1376,13 +1382,13 @@
       <c r="C21" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="40" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E21" s="39" t="n">
+      <c r="E21" s="40" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F21" s="39" t="n">
+      <c r="F21" s="40" t="n">
         <v>46307.08333333334</v>
       </c>
       <c r="G21" s="24">
@@ -1414,13 +1420,13 @@
       <c r="C22" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="40" t="n">
         <v>46302.79166666666</v>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="40" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="F22" s="39" t="n">
+      <c r="F22" s="40" t="n">
         <v>46304.08333333334</v>
       </c>
       <c r="G22" s="24">
@@ -1489,10 +1495,10 @@
         </is>
       </c>
       <c r="C27" s="38" t="n"/>
-      <c r="D27" s="40" t="n">
+      <c r="D27" s="41" t="n">
         <v>46299</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E27" s="41" t="n">
         <v>46319</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -1517,10 +1523,10 @@
         </is>
       </c>
       <c r="C28" s="38" t="n"/>
-      <c r="D28" s="40" t="n">
+      <c r="D28" s="41" t="n">
         <v>46300</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E28" s="41" t="n">
         <v>46313</v>
       </c>
       <c r="F28" s="16" t="inlineStr">

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -244,6 +244,12 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -264,12 +270,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/08-10-2026/PAT_Berth_Window.xlsx
+++ b/08-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -736,13 +745,13 @@
       <c r="C4" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46303.5</v>
       </c>
       <c r="G4" s="24">
@@ -774,13 +783,13 @@
       <c r="C5" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46302.41666666666</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="43" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="43" t="n">
         <v>46304.58333333334</v>
       </c>
       <c r="G5" s="24">
@@ -812,13 +821,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46303.75</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="43" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="43" t="n">
         <v>46305.625</v>
       </c>
       <c r="G6" s="24">
@@ -850,13 +859,13 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="43" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="43" t="n">
         <v>46306.625</v>
       </c>
       <c r="G7" s="24">
@@ -888,13 +897,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="43" t="n">
         <v>46300.875</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="43" t="n">
         <v>46301.54166666666</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="43" t="n">
         <v>46303.54166666666</v>
       </c>
       <c r="G8" s="24">
@@ -926,13 +935,13 @@
       <c r="C9" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="43" t="n">
         <v>46302.625</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="43" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="43" t="n">
         <v>46304.70833333334</v>
       </c>
       <c r="G9" s="24">
@@ -964,13 +973,13 @@
       <c r="C10" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="43" t="n">
         <v>46304.375</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="43" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="43" t="n">
         <v>46306.58333333334</v>
       </c>
       <c r="G10" s="24">
@@ -1002,13 +1011,13 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>46301.875</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="43" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="43" t="n">
         <v>46303.54166666666</v>
       </c>
       <c r="G11" s="24">
@@ -1040,13 +1049,13 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="43" t="n">
         <v>46303.58333333334</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="43" t="n">
         <v>46304.58333333334</v>
       </c>
       <c r="G12" s="24">
@@ -1078,13 +1087,13 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="43" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="43" t="n">
         <v>46306.04166666666</v>
       </c>
       <c r="G13" s="24">
@@ -1116,13 +1125,13 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="43" t="n">
         <v>46306.16666666666</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="43" t="n">
         <v>46307.54166666666</v>
       </c>
       <c r="G14" s="24">
@@ -1154,13 +1163,13 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="43" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="43" t="n">
         <v>46304.08333333334</v>
       </c>
       <c r="G15" s="24">
@@ -1192,13 +1201,13 @@
       <c r="C16" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="43" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="43" t="n">
         <v>46304.08333333334</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="43" t="n">
         <v>46305.54166666666</v>
       </c>
       <c r="G16" s="24">
@@ -1230,13 +1239,13 @@
       <c r="C17" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="43" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E17" s="43" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="43" t="n">
         <v>46306.25</v>
       </c>
       <c r="G17" s="24">
@@ -1268,13 +1277,13 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="43" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="43" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="43" t="n">
         <v>46307.58333333334</v>
       </c>
       <c r="G18" s="24">
@@ -1306,13 +1315,13 @@
       <c r="C19" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="40" t="n">
+      <c r="D19" s="43" t="n">
         <v>46302.54166666666</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E19" s="43" t="n">
         <v>46302.58333333334</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="43" t="n">
         <v>46304.54166666666</v>
       </c>
       <c r="G19" s="24">
@@ -1344,13 +1353,13 @@
       <c r="C20" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="43" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="43" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="43" t="n">
         <v>46306.125</v>
       </c>
       <c r="G20" s="24">
@@ -1382,13 +1391,13 @@
       <c r="C21" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="43" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E21" s="43" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="43" t="n">
         <v>46307.08333333334</v>
       </c>
       <c r="G21" s="24">
@@ -1420,13 +1429,13 @@
       <c r="C22" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D22" s="40" t="n">
+      <c r="D22" s="43" t="n">
         <v>46302.79166666666</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E22" s="43" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="43" t="n">
         <v>46304.08333333334</v>
       </c>
       <c r="G22" s="24">
@@ -1445,7 +1454,7 @@
       <c r="J22" s="23" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1478,10 +1487,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="36" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="39" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -1494,11 +1503,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="41" t="n">
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="44" t="n">
         <v>46299</v>
       </c>
-      <c r="E27" s="41" t="n">
+      <c r="E27" s="44" t="n">
         <v>46319</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -1506,10 +1515,10 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (MTT BANGKOK has been alongside at 20D since 07/14, HE JIN shifts in on 09/02)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G27" s="35" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
-      <c r="J27" s="36" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="39" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -1522,11 +1531,11 @@
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="41" t="n">
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="44" t="n">
         <v>46300</v>
       </c>
-      <c r="E28" s="41" t="n">
+      <c r="E28" s="44" t="n">
         <v>46313</v>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -1534,10 +1543,10 @@
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G28" s="35" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="35" t="n"/>
-      <c r="J28" s="36" t="n"/>
+      <c r="G28" s="38" t="n"/>
+      <c r="H28" s="38" t="n"/>
+      <c r="I28" s="38" t="n"/>
+      <c r="J28" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
